--- a/site/mb_leads.xlsx
+++ b/site/mb_leads.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Manitoba" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Manitoba" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/site/mb_leads.xlsx
+++ b/site/mb_leads.xlsx
@@ -618,7 +618,7 @@
         <v>325</v>
       </c>
       <c r="U2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V2" t="n">
         <v>54.44006</v>
@@ -686,7 +686,7 @@
         <v>300</v>
       </c>
       <c r="U3" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V3" t="n">
         <v>54.41652</v>
@@ -754,7 +754,7 @@
         <v>325</v>
       </c>
       <c r="U4" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V4" t="n">
         <v>54.40588</v>
@@ -822,7 +822,7 @@
         <v>250</v>
       </c>
       <c r="U5" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V5" t="n">
         <v>54.4023</v>
@@ -890,7 +890,7 @@
         <v>325</v>
       </c>
       <c r="U6" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V6" t="n">
         <v>54.38865</v>
@@ -958,7 +958,7 @@
         <v>325</v>
       </c>
       <c r="U7" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V7" t="n">
         <v>54.38262</v>
@@ -1026,7 +1026,7 @@
         <v>325</v>
       </c>
       <c r="U8" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V8" t="n">
         <v>54.3774</v>
@@ -1094,7 +1094,7 @@
         <v>325</v>
       </c>
       <c r="U9" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V9" t="n">
         <v>54.35013</v>
@@ -1162,7 +1162,7 @@
         <v>325</v>
       </c>
       <c r="U10" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V10" t="n">
         <v>54.31774</v>
@@ -1230,7 +1230,7 @@
         <v>325</v>
       </c>
       <c r="U11" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V11" t="n">
         <v>54.30433</v>
@@ -1298,7 +1298,7 @@
         <v>325</v>
       </c>
       <c r="U12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V12" t="n">
         <v>54.31095</v>
@@ -1366,7 +1366,7 @@
         <v>325</v>
       </c>
       <c r="U13" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V13" t="n">
         <v>54.29223</v>
@@ -1434,7 +1434,7 @@
         <v>325</v>
       </c>
       <c r="U14" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V14" t="n">
         <v>54.28877</v>
@@ -1502,7 +1502,7 @@
         <v>325</v>
       </c>
       <c r="U15" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V15" t="n">
         <v>54.27119</v>
@@ -1570,7 +1570,7 @@
         <v>325</v>
       </c>
       <c r="U16" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V16" t="n">
         <v>54.48531</v>
@@ -1638,7 +1638,7 @@
         <v>325</v>
       </c>
       <c r="U17" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V17" t="n">
         <v>54.47917</v>
@@ -1706,7 +1706,7 @@
         <v>325</v>
       </c>
       <c r="U18" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V18" t="n">
         <v>54.46575</v>
@@ -1774,7 +1774,7 @@
         <v>325</v>
       </c>
       <c r="U19" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V19" t="n">
         <v>54.4612</v>
@@ -1842,7 +1842,7 @@
         <v>325</v>
       </c>
       <c r="U20" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V20" t="n">
         <v>54.47043</v>
@@ -1910,7 +1910,7 @@
         <v>325</v>
       </c>
       <c r="U21" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V21" t="n">
         <v>54.48482</v>
@@ -1978,7 +1978,7 @@
         <v>325</v>
       </c>
       <c r="U22" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V22" t="n">
         <v>54.48077</v>
@@ -2046,7 +2046,7 @@
         <v>325</v>
       </c>
       <c r="U23" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V23" t="n">
         <v>54.46429</v>
@@ -2114,7 +2114,7 @@
         <v>325</v>
       </c>
       <c r="U24" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V24" t="n">
         <v>54.4446</v>
@@ -2182,7 +2182,7 @@
         <v>325</v>
       </c>
       <c r="U25" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V25" t="n">
         <v>54.43692</v>
@@ -2254,7 +2254,7 @@
         <v>325</v>
       </c>
       <c r="U26" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V26" t="n">
         <v>54.57623</v>
@@ -2326,7 +2326,7 @@
         <v>325</v>
       </c>
       <c r="U27" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V27" t="n">
         <v>54.62116</v>
@@ -2398,7 +2398,7 @@
         <v>325</v>
       </c>
       <c r="U28" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V28" t="n">
         <v>54.68833</v>
@@ -2470,7 +2470,7 @@
         <v>325</v>
       </c>
       <c r="U29" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V29" t="n">
         <v>54.68398</v>
@@ -2542,7 +2542,7 @@
         <v>325</v>
       </c>
       <c r="U30" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V30" t="n">
         <v>54.67871</v>
@@ -2614,7 +2614,7 @@
         <v>325</v>
       </c>
       <c r="U31" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V31" t="n">
         <v>54.69795</v>
@@ -2686,7 +2686,7 @@
         <v>325</v>
       </c>
       <c r="U32" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V32" t="n">
         <v>54.6869</v>
@@ -2758,7 +2758,7 @@
         <v>325</v>
       </c>
       <c r="U33" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V33" t="n">
         <v>54.67641</v>
@@ -2830,7 +2830,7 @@
         <v>325</v>
       </c>
       <c r="U34" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V34" t="n">
         <v>54.66954</v>
@@ -2902,7 +2902,7 @@
         <v>325</v>
       </c>
       <c r="U35" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V35" t="n">
         <v>54.70173</v>
@@ -2974,7 +2974,7 @@
         <v>325</v>
       </c>
       <c r="U36" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V36" t="n">
         <v>54.74888</v>
@@ -3046,7 +3046,7 @@
         <v>325</v>
       </c>
       <c r="U37" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V37" t="n">
         <v>54.6709</v>
@@ -3114,7 +3114,7 @@
         <v>325</v>
       </c>
       <c r="U38" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V38" t="n">
         <v>54.64084</v>
@@ -3182,7 +3182,7 @@
         <v>325</v>
       </c>
       <c r="U39" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V39" t="n">
         <v>54.66079</v>
@@ -3250,7 +3250,7 @@
         <v>325</v>
       </c>
       <c r="U40" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V40" t="n">
         <v>54.65198</v>
@@ -3318,7 +3318,7 @@
         <v>325</v>
       </c>
       <c r="U41" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V41" t="n">
         <v>54.62008</v>
@@ -3386,7 +3386,7 @@
         <v>325</v>
       </c>
       <c r="U42" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V42" t="n">
         <v>54.6836</v>
@@ -3454,7 +3454,7 @@
         <v>325</v>
       </c>
       <c r="U43" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V43" t="n">
         <v>54.67125</v>
@@ -3526,7 +3526,7 @@
         <v>325</v>
       </c>
       <c r="U44" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V44" t="n">
         <v>54.70521</v>
@@ -3594,7 +3594,7 @@
         <v>325</v>
       </c>
       <c r="U45" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V45" t="n">
         <v>54.7312</v>
@@ -3662,7 +3662,7 @@
         <v>325</v>
       </c>
       <c r="U46" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V46" t="n">
         <v>54.74522</v>
@@ -3730,7 +3730,7 @@
         <v>325</v>
       </c>
       <c r="U47" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V47" t="n">
         <v>54.69832</v>
@@ -3798,7 +3798,7 @@
         <v>325</v>
       </c>
       <c r="U48" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V48" t="n">
         <v>54.73689</v>
@@ -3866,7 +3866,7 @@
         <v>325</v>
       </c>
       <c r="U49" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V49" t="n">
         <v>54.70234</v>
@@ -3938,7 +3938,7 @@
         <v>325</v>
       </c>
       <c r="U50" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V50" t="n">
         <v>54.74026</v>
@@ -4006,7 +4006,7 @@
         <v>325</v>
       </c>
       <c r="U51" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V51" t="n">
         <v>54.57242</v>
@@ -4074,7 +4074,7 @@
         <v>325</v>
       </c>
       <c r="U52" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V52" t="n">
         <v>54.61727</v>
@@ -4142,7 +4142,7 @@
         <v>325</v>
       </c>
       <c r="U53" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V53" t="n">
         <v>54.53781</v>
@@ -4210,7 +4210,7 @@
         <v>325</v>
       </c>
       <c r="U54" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V54" t="n">
         <v>54.57229</v>
@@ -4278,7 +4278,7 @@
         <v>325</v>
       </c>
       <c r="U55" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V55" t="n">
         <v>54.57473</v>
@@ -4346,7 +4346,7 @@
         <v>325</v>
       </c>
       <c r="U56" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V56" t="n">
         <v>54.60199</v>
@@ -4414,7 +4414,7 @@
         <v>325</v>
       </c>
       <c r="U57" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V57" t="n">
         <v>54.53244</v>
@@ -4482,7 +4482,7 @@
         <v>325</v>
       </c>
       <c r="U58" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V58" t="n">
         <v>54.58539</v>
@@ -4550,7 +4550,7 @@
         <v>325</v>
       </c>
       <c r="U59" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V59" t="n">
         <v>54.5734</v>
@@ -4618,7 +4618,7 @@
         <v>325</v>
       </c>
       <c r="U60" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V60" t="n">
         <v>54.5075</v>
@@ -4686,7 +4686,7 @@
         <v>325</v>
       </c>
       <c r="U61" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V61" t="n">
         <v>54.61209</v>
@@ -4754,7 +4754,7 @@
         <v>325</v>
       </c>
       <c r="U62" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V62" t="n">
         <v>54.6823</v>
@@ -4822,7 +4822,7 @@
         <v>325</v>
       </c>
       <c r="U63" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V63" t="n">
         <v>54.72712</v>
@@ -4890,7 +4890,7 @@
         <v>325</v>
       </c>
       <c r="U64" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V64" t="n">
         <v>54.64165</v>
@@ -4958,7 +4958,7 @@
         <v>325</v>
       </c>
       <c r="U65" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V65" t="n">
         <v>54.59793</v>
@@ -5030,7 +5030,7 @@
         <v>325</v>
       </c>
       <c r="U66" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V66" t="n">
         <v>54.69399</v>
@@ -5098,7 +5098,7 @@
         <v>250</v>
       </c>
       <c r="U67" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V67" t="n">
         <v>54.7161</v>
@@ -5166,7 +5166,7 @@
         <v>325</v>
       </c>
       <c r="U68" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V68" t="n">
         <v>54.72683</v>
@@ -5234,7 +5234,7 @@
         <v>325</v>
       </c>
       <c r="U69" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V69" t="n">
         <v>54.74147</v>
@@ -5306,7 +5306,7 @@
         <v>325</v>
       </c>
       <c r="U70" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V70" t="n">
         <v>54.72959</v>
@@ -5378,7 +5378,7 @@
         <v>325</v>
       </c>
       <c r="U71" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V71" t="n">
         <v>54.74109</v>
@@ -5446,7 +5446,7 @@
         <v>325</v>
       </c>
       <c r="U72" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V72" t="n">
         <v>54.74539</v>
@@ -5514,7 +5514,7 @@
         <v>325</v>
       </c>
       <c r="U73" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V73" t="n">
         <v>54.72402</v>
@@ -5582,7 +5582,7 @@
         <v>325</v>
       </c>
       <c r="U74" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V74" t="n">
         <v>54.66852</v>
@@ -5650,7 +5650,7 @@
         <v>325</v>
       </c>
       <c r="U75" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V75" t="n">
         <v>54.64644</v>
@@ -5718,7 +5718,7 @@
         <v>325</v>
       </c>
       <c r="U76" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V76" t="n">
         <v>54.65788</v>
@@ -5786,7 +5786,7 @@
         <v>325</v>
       </c>
       <c r="U77" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V77" t="n">
         <v>54.63609</v>
@@ -5858,7 +5858,7 @@
         <v>325</v>
       </c>
       <c r="U78" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V78" t="n">
         <v>54.61165</v>
@@ -5926,7 +5926,7 @@
         <v>325</v>
       </c>
       <c r="U79" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V79" t="n">
         <v>54.60441</v>
@@ -5994,7 +5994,7 @@
         <v>325</v>
       </c>
       <c r="U80" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V80" t="n">
         <v>54.69608</v>
@@ -6062,7 +6062,7 @@
         <v>325</v>
       </c>
       <c r="U81" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V81" t="n">
         <v>54.69727</v>
@@ -6134,7 +6134,7 @@
         <v>325</v>
       </c>
       <c r="U82" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V82" t="n">
         <v>54.68107</v>
@@ -6206,7 +6206,7 @@
         <v>325</v>
       </c>
       <c r="U83" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V83" t="n">
         <v>54.62832</v>
@@ -6278,7 +6278,7 @@
         <v>325</v>
       </c>
       <c r="U84" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V84" t="n">
         <v>54.638</v>
@@ -6350,7 +6350,7 @@
         <v>325</v>
       </c>
       <c r="U85" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V85" t="n">
         <v>54.63177</v>
@@ -6418,7 +6418,7 @@
         <v>325</v>
       </c>
       <c r="U86" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V86" t="n">
         <v>54.59067</v>
@@ -6486,7 +6486,7 @@
         <v>325</v>
       </c>
       <c r="U87" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V87" t="n">
         <v>54.64082</v>
@@ -6554,7 +6554,7 @@
         <v>325</v>
       </c>
       <c r="U88" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V88" t="n">
         <v>54.71363</v>
@@ -6622,7 +6622,7 @@
         <v>325</v>
       </c>
       <c r="U89" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V89" t="n">
         <v>54.6876</v>
@@ -6690,7 +6690,7 @@
         <v>325</v>
       </c>
       <c r="U90" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V90" t="n">
         <v>54.6949</v>
@@ -6758,7 +6758,7 @@
         <v>325</v>
       </c>
       <c r="U91" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V91" t="n">
         <v>54.68269</v>
@@ -6826,7 +6826,7 @@
         <v>325</v>
       </c>
       <c r="U92" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V92" t="n">
         <v>54.70084</v>
@@ -6894,7 +6894,7 @@
         <v>325</v>
       </c>
       <c r="U93" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V93" t="n">
         <v>54.6858</v>
@@ -6966,7 +6966,7 @@
         <v>325</v>
       </c>
       <c r="U94" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V94" t="n">
         <v>54.67947</v>
@@ -7038,7 +7038,7 @@
         <v>325</v>
       </c>
       <c r="U95" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V95" t="n">
         <v>54.65981</v>
@@ -7070,7 +7070,7 @@
       <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Platinum</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -7110,7 +7110,7 @@
         <v>325</v>
       </c>
       <c r="U96" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V96" t="n">
         <v>54.6344</v>
@@ -7178,7 +7178,7 @@
         <v>325</v>
       </c>
       <c r="U97" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V97" t="n">
         <v>54.60461</v>
@@ -7246,7 +7246,7 @@
         <v>325</v>
       </c>
       <c r="U98" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V98" t="n">
         <v>54.68004</v>
@@ -7314,7 +7314,7 @@
         <v>325</v>
       </c>
       <c r="U99" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V99" t="n">
         <v>54.7485</v>
@@ -7382,7 +7382,7 @@
         <v>325</v>
       </c>
       <c r="U100" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V100" t="n">
         <v>54.74569</v>
@@ -7450,7 +7450,7 @@
         <v>325</v>
       </c>
       <c r="U101" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V101" t="n">
         <v>54.7414</v>
@@ -7518,7 +7518,7 @@
         <v>325</v>
       </c>
       <c r="U102" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V102" t="n">
         <v>54.54296</v>
@@ -7586,7 +7586,7 @@
         <v>325</v>
       </c>
       <c r="U103" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V103" t="n">
         <v>54.51409</v>
@@ -7654,7 +7654,7 @@
         <v>325</v>
       </c>
       <c r="U104" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V104" t="n">
         <v>54.57777</v>
@@ -7722,7 +7722,7 @@
         <v>325</v>
       </c>
       <c r="U105" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V105" t="n">
         <v>54.59713</v>
@@ -7790,7 +7790,7 @@
         <v>325</v>
       </c>
       <c r="U106" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V106" t="n">
         <v>54.64324</v>
@@ -7858,7 +7858,7 @@
         <v>325</v>
       </c>
       <c r="U107" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V107" t="n">
         <v>54.6628</v>
@@ -7926,7 +7926,7 @@
         <v>325</v>
       </c>
       <c r="U108" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V108" t="n">
         <v>54.65841</v>
@@ -7998,7 +7998,7 @@
         <v>325</v>
       </c>
       <c r="U109" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V109" t="n">
         <v>54.70189</v>
@@ -8066,7 +8066,7 @@
         <v>325</v>
       </c>
       <c r="U110" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V110" t="n">
         <v>54.71998</v>
@@ -8138,7 +8138,7 @@
         <v>325</v>
       </c>
       <c r="U111" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V111" t="n">
         <v>54.97997</v>
@@ -8210,7 +8210,7 @@
         <v>325</v>
       </c>
       <c r="U112" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V112" t="n">
         <v>54.98074</v>
@@ -8282,7 +8282,7 @@
         <v>325</v>
       </c>
       <c r="U113" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V113" t="n">
         <v>54.97034</v>
@@ -8354,7 +8354,7 @@
         <v>325</v>
       </c>
       <c r="U114" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V114" t="n">
         <v>54.96918</v>
@@ -8426,7 +8426,7 @@
         <v>325</v>
       </c>
       <c r="U115" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V115" t="n">
         <v>54.97111</v>
@@ -8494,7 +8494,7 @@
         <v>300</v>
       </c>
       <c r="U116" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V116" t="n">
         <v>54.95835</v>
@@ -8562,7 +8562,7 @@
         <v>325</v>
       </c>
       <c r="U117" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V117" t="n">
         <v>54.90646</v>
@@ -8630,7 +8630,7 @@
         <v>325</v>
       </c>
       <c r="U118" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V118" t="n">
         <v>54.8999</v>
@@ -8702,7 +8702,7 @@
         <v>325</v>
       </c>
       <c r="U119" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V119" t="n">
         <v>54.96039</v>
@@ -8774,7 +8774,7 @@
         <v>250</v>
       </c>
       <c r="U120" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V120" t="n">
         <v>54.99582</v>
@@ -8842,7 +8842,7 @@
         <v>325</v>
       </c>
       <c r="U121" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V121" t="n">
         <v>54.9834</v>
@@ -8914,7 +8914,7 @@
         <v>325</v>
       </c>
       <c r="U122" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V122" t="n">
         <v>54.93243</v>
@@ -8986,7 +8986,7 @@
         <v>325</v>
       </c>
       <c r="U123" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V123" t="n">
         <v>54.9297</v>
@@ -9054,7 +9054,7 @@
         <v>325</v>
       </c>
       <c r="U124" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V124" t="n">
         <v>54.83817</v>
@@ -9122,7 +9122,7 @@
         <v>325</v>
       </c>
       <c r="U125" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V125" t="n">
         <v>54.87728</v>
@@ -9190,7 +9190,7 @@
         <v>325</v>
       </c>
       <c r="U126" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V126" t="n">
         <v>54.86774</v>
@@ -9262,7 +9262,7 @@
         <v>325</v>
       </c>
       <c r="U127" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V127" t="n">
         <v>54.81736</v>
@@ -9334,7 +9334,7 @@
         <v>325</v>
       </c>
       <c r="U128" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V128" t="n">
         <v>54.77007</v>
@@ -9402,7 +9402,7 @@
         <v>325</v>
       </c>
       <c r="U129" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V129" t="n">
         <v>54.83014</v>
@@ -9470,7 +9470,7 @@
         <v>250</v>
       </c>
       <c r="U130" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V130" t="n">
         <v>54.89008</v>
@@ -9538,7 +9538,7 @@
         <v>325</v>
       </c>
       <c r="U131" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V131" t="n">
         <v>54.92137</v>
@@ -9606,7 +9606,7 @@
         <v>325</v>
       </c>
       <c r="U132" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V132" t="n">
         <v>54.91592</v>
@@ -9674,7 +9674,7 @@
         <v>325</v>
       </c>
       <c r="U133" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V133" t="n">
         <v>54.90975</v>
@@ -9742,7 +9742,7 @@
         <v>325</v>
       </c>
       <c r="U134" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V134" t="n">
         <v>54.88434</v>
@@ -9814,7 +9814,7 @@
         <v>325</v>
       </c>
       <c r="U135" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V135" t="n">
         <v>54.8809</v>
@@ -9886,7 +9886,7 @@
         <v>325</v>
       </c>
       <c r="U136" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V136" t="n">
         <v>54.8784</v>
@@ -9954,7 +9954,7 @@
         <v>325</v>
       </c>
       <c r="U137" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V137" t="n">
         <v>54.87334</v>
@@ -10022,7 +10022,7 @@
         <v>325</v>
       </c>
       <c r="U138" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V138" t="n">
         <v>54.98142</v>
@@ -10090,7 +10090,7 @@
         <v>325</v>
       </c>
       <c r="U139" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V139" t="n">
         <v>54.88262</v>
@@ -10158,7 +10158,7 @@
         <v>325</v>
       </c>
       <c r="U140" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V140" t="n">
         <v>54.86966</v>
@@ -10226,7 +10226,7 @@
         <v>325</v>
       </c>
       <c r="U141" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V141" t="n">
         <v>54.87633</v>
@@ -10294,7 +10294,7 @@
         <v>325</v>
       </c>
       <c r="U142" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V142" t="n">
         <v>54.96272</v>
@@ -10362,7 +10362,7 @@
         <v>325</v>
       </c>
       <c r="U143" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V143" t="n">
         <v>54.86981</v>
@@ -10430,7 +10430,7 @@
         <v>325</v>
       </c>
       <c r="U144" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V144" t="n">
         <v>54.89168</v>
@@ -10498,7 +10498,7 @@
         <v>250</v>
       </c>
       <c r="U145" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V145" t="n">
         <v>54.80946</v>
@@ -10566,7 +10566,7 @@
         <v>325</v>
       </c>
       <c r="U146" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V146" t="n">
         <v>54.81987</v>
@@ -10638,7 +10638,7 @@
         <v>325</v>
       </c>
       <c r="U147" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V147" t="n">
         <v>54.82889</v>
@@ -10706,7 +10706,7 @@
         <v>325</v>
       </c>
       <c r="U148" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V148" t="n">
         <v>54.90912</v>
@@ -10774,7 +10774,7 @@
         <v>325</v>
       </c>
       <c r="U149" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V149" t="n">
         <v>54.84012</v>
@@ -10842,7 +10842,7 @@
         <v>325</v>
       </c>
       <c r="U150" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V150" t="n">
         <v>54.83085</v>
@@ -10910,7 +10910,7 @@
         <v>325</v>
       </c>
       <c r="U151" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V151" t="n">
         <v>54.83082</v>
@@ -10978,7 +10978,7 @@
         <v>300</v>
       </c>
       <c r="U152" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V152" t="n">
         <v>54.82931</v>
@@ -11046,7 +11046,7 @@
         <v>325</v>
       </c>
       <c r="U153" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V153" t="n">
         <v>54.92728</v>
@@ -11118,7 +11118,7 @@
         <v>325</v>
       </c>
       <c r="U154" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V154" t="n">
         <v>54.82856</v>
@@ -11186,7 +11186,7 @@
         <v>325</v>
       </c>
       <c r="U155" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V155" t="n">
         <v>54.78298</v>
@@ -11254,7 +11254,7 @@
         <v>325</v>
       </c>
       <c r="U156" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V156" t="n">
         <v>54.75399</v>
@@ -11322,7 +11322,7 @@
         <v>325</v>
       </c>
       <c r="U157" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V157" t="n">
         <v>54.75865</v>
@@ -11390,7 +11390,7 @@
         <v>325</v>
       </c>
       <c r="U158" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V158" t="n">
         <v>54.76349</v>
@@ -11458,7 +11458,7 @@
         <v>325</v>
       </c>
       <c r="U159" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V159" t="n">
         <v>54.871</v>
@@ -11530,7 +11530,7 @@
         <v>300</v>
       </c>
       <c r="U160" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V160" t="n">
         <v>54.99388</v>
@@ -11598,7 +11598,7 @@
         <v>325</v>
       </c>
       <c r="U161" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V161" t="n">
         <v>54.83301</v>
@@ -11670,7 +11670,7 @@
         <v>325</v>
       </c>
       <c r="U162" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V162" t="n">
         <v>54.88217</v>
@@ -11742,7 +11742,7 @@
         <v>325</v>
       </c>
       <c r="U163" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V163" t="n">
         <v>54.97355</v>
@@ -11810,7 +11810,7 @@
         <v>325</v>
       </c>
       <c r="U164" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V164" t="n">
         <v>54.90602</v>
@@ -11878,7 +11878,7 @@
         <v>325</v>
       </c>
       <c r="U165" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V165" t="n">
         <v>54.90188</v>
@@ -11946,7 +11946,7 @@
         <v>325</v>
       </c>
       <c r="U166" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V166" t="n">
         <v>54.90817</v>
@@ -12014,7 +12014,7 @@
         <v>325</v>
       </c>
       <c r="U167" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V167" t="n">
         <v>54.98316</v>
@@ -12082,7 +12082,7 @@
         <v>325</v>
       </c>
       <c r="U168" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V168" t="n">
         <v>54.97737</v>
@@ -12150,7 +12150,7 @@
         <v>325</v>
       </c>
       <c r="U169" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V169" t="n">
         <v>54.8289</v>
@@ -12218,7 +12218,7 @@
         <v>325</v>
       </c>
       <c r="U170" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V170" t="n">
         <v>54.96298</v>
@@ -12286,7 +12286,7 @@
         <v>325</v>
       </c>
       <c r="U171" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V171" t="n">
         <v>54.89112</v>
@@ -12354,7 +12354,7 @@
         <v>300</v>
       </c>
       <c r="U172" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V172" t="n">
         <v>54.80452</v>
@@ -12422,7 +12422,7 @@
         <v>325</v>
       </c>
       <c r="U173" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V173" t="n">
         <v>54.80069</v>
@@ -12490,7 +12490,7 @@
         <v>325</v>
       </c>
       <c r="U174" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V174" t="n">
         <v>54.80438</v>
@@ -12562,7 +12562,7 @@
         <v>325</v>
       </c>
       <c r="U175" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V175" t="n">
         <v>54.84309</v>
@@ -12634,7 +12634,7 @@
         <v>325</v>
       </c>
       <c r="U176" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V176" t="n">
         <v>54.79436</v>
@@ -12706,7 +12706,7 @@
         <v>325</v>
       </c>
       <c r="U177" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V177" t="n">
         <v>54.78744</v>
@@ -12778,7 +12778,7 @@
         <v>325</v>
       </c>
       <c r="U178" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V178" t="n">
         <v>54.79682</v>
@@ -12850,7 +12850,7 @@
         <v>325</v>
       </c>
       <c r="U179" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V179" t="n">
         <v>54.7701</v>
@@ -12922,7 +12922,7 @@
         <v>325</v>
       </c>
       <c r="U180" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V180" t="n">
         <v>54.82663</v>
@@ -12994,7 +12994,7 @@
         <v>325</v>
       </c>
       <c r="U181" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V181" t="n">
         <v>54.80487</v>
@@ -13066,7 +13066,7 @@
         <v>325</v>
       </c>
       <c r="U182" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V182" t="n">
         <v>54.83072</v>
@@ -13138,7 +13138,7 @@
         <v>325</v>
       </c>
       <c r="U183" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V183" t="n">
         <v>54.75921</v>
@@ -13210,7 +13210,7 @@
         <v>325</v>
       </c>
       <c r="U184" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V184" t="n">
         <v>54.83216</v>
@@ -13282,7 +13282,7 @@
         <v>250</v>
       </c>
       <c r="U185" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V185" t="n">
         <v>54.85718</v>
@@ -13354,7 +13354,7 @@
         <v>325</v>
       </c>
       <c r="U186" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V186" t="n">
         <v>54.85277</v>
@@ -13426,7 +13426,7 @@
         <v>325</v>
       </c>
       <c r="U187" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V187" t="n">
         <v>54.85548</v>
@@ -13494,7 +13494,7 @@
         <v>325</v>
       </c>
       <c r="U188" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V188" t="n">
         <v>54.84866</v>
@@ -13566,7 +13566,7 @@
         <v>325</v>
       </c>
       <c r="U189" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V189" t="n">
         <v>54.84497</v>
@@ -13638,7 +13638,7 @@
         <v>325</v>
       </c>
       <c r="U190" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V190" t="n">
         <v>54.96239</v>
@@ -13710,7 +13710,7 @@
         <v>325</v>
       </c>
       <c r="U191" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V191" t="n">
         <v>54.79167</v>
@@ -13778,7 +13778,7 @@
         <v>325</v>
       </c>
       <c r="U192" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V192" t="n">
         <v>54.84484</v>
@@ -13846,7 +13846,7 @@
         <v>325</v>
       </c>
       <c r="U193" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V193" t="n">
         <v>54.81239</v>
@@ -13914,7 +13914,7 @@
         <v>325</v>
       </c>
       <c r="U194" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V194" t="n">
         <v>54.80899</v>
@@ -13982,7 +13982,7 @@
         <v>325</v>
       </c>
       <c r="U195" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V195" t="n">
         <v>54.80826</v>
@@ -14050,7 +14050,7 @@
         <v>325</v>
       </c>
       <c r="U196" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V196" t="n">
         <v>54.98687</v>
@@ -14118,7 +14118,7 @@
         <v>325</v>
       </c>
       <c r="U197" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V197" t="n">
         <v>54.81715</v>
@@ -14186,7 +14186,7 @@
         <v>325</v>
       </c>
       <c r="U198" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V198" t="n">
         <v>54.92387</v>
@@ -14254,7 +14254,7 @@
         <v>325</v>
       </c>
       <c r="U199" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V199" t="n">
         <v>54.90889</v>
@@ -14322,7 +14322,7 @@
         <v>325</v>
       </c>
       <c r="U200" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V200" t="n">
         <v>54.90269</v>
@@ -14390,7 +14390,7 @@
         <v>325</v>
       </c>
       <c r="U201" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V201" t="n">
         <v>54.76196</v>
@@ -14458,7 +14458,7 @@
         <v>325</v>
       </c>
       <c r="U202" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V202" t="n">
         <v>54.93107</v>
@@ -14526,7 +14526,7 @@
         <v>300</v>
       </c>
       <c r="U203" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V203" t="n">
         <v>54.87823</v>
@@ -14594,7 +14594,7 @@
         <v>325</v>
       </c>
       <c r="U204" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V204" t="n">
         <v>54.88835</v>
@@ -14662,7 +14662,7 @@
         <v>325</v>
       </c>
       <c r="U205" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V205" t="n">
         <v>54.88193</v>
@@ -14730,7 +14730,7 @@
         <v>325</v>
       </c>
       <c r="U206" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V206" t="n">
         <v>54.89241</v>
@@ -14798,7 +14798,7 @@
         <v>325</v>
       </c>
       <c r="U207" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V207" t="n">
         <v>54.90243</v>
@@ -14866,7 +14866,7 @@
         <v>325</v>
       </c>
       <c r="U208" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V208" t="n">
         <v>54.91736</v>
@@ -14938,7 +14938,7 @@
         <v>325</v>
       </c>
       <c r="U209" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V209" t="n">
         <v>54.81098</v>
@@ -15010,7 +15010,7 @@
         <v>325</v>
       </c>
       <c r="U210" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V210" t="n">
         <v>54.81096</v>
@@ -15078,7 +15078,7 @@
         <v>325</v>
       </c>
       <c r="U211" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V211" t="n">
         <v>54.91767</v>
@@ -15146,7 +15146,7 @@
         <v>325</v>
       </c>
       <c r="U212" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V212" t="n">
         <v>54.79192</v>
@@ -15214,7 +15214,7 @@
         <v>325</v>
       </c>
       <c r="U213" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V213" t="n">
         <v>54.79734</v>
@@ -15282,7 +15282,7 @@
         <v>325</v>
       </c>
       <c r="U214" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V214" t="n">
         <v>54.82008</v>
@@ -15350,7 +15350,7 @@
         <v>325</v>
       </c>
       <c r="U215" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V215" t="n">
         <v>54.83757</v>
@@ -15418,7 +15418,7 @@
         <v>325</v>
       </c>
       <c r="U216" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V216" t="n">
         <v>54.95531</v>
@@ -15490,7 +15490,7 @@
         <v>325</v>
       </c>
       <c r="U217" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V217" t="n">
         <v>54.81384</v>
@@ -15522,7 +15522,7 @@
       <c r="E218" t="inlineStr"/>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Lithium</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
@@ -15562,7 +15562,7 @@
         <v>325</v>
       </c>
       <c r="U218" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V218" t="n">
         <v>54.85117</v>
@@ -15594,7 +15594,7 @@
       <c r="E219" t="inlineStr"/>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Beryllium</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
@@ -15634,7 +15634,7 @@
         <v>325</v>
       </c>
       <c r="U219" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V219" t="n">
         <v>54.84344</v>
@@ -15666,7 +15666,7 @@
       <c r="E220" t="inlineStr"/>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Beryllium</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
@@ -15706,7 +15706,7 @@
         <v>325</v>
       </c>
       <c r="U220" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V220" t="n">
         <v>54.85577</v>
@@ -15774,7 +15774,7 @@
         <v>325</v>
       </c>
       <c r="U221" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V221" t="n">
         <v>54.807</v>
@@ -15842,7 +15842,7 @@
         <v>325</v>
       </c>
       <c r="U222" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V222" t="n">
         <v>54.78834</v>
@@ -15910,7 +15910,7 @@
         <v>325</v>
       </c>
       <c r="U223" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V223" t="n">
         <v>54.81376</v>
@@ -15982,7 +15982,7 @@
         <v>325</v>
       </c>
       <c r="U224" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V224" t="n">
         <v>54.80189</v>
@@ -16050,7 +16050,7 @@
         <v>325</v>
       </c>
       <c r="U225" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V225" t="n">
         <v>54.80143</v>
@@ -16122,7 +16122,7 @@
         <v>325</v>
       </c>
       <c r="U226" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V226" t="n">
         <v>54.83119</v>
@@ -16194,7 +16194,7 @@
         <v>325</v>
       </c>
       <c r="U227" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V227" t="n">
         <v>54.79824</v>
@@ -16262,7 +16262,7 @@
         <v>325</v>
       </c>
       <c r="U228" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V228" t="n">
         <v>54.79949</v>
@@ -16330,7 +16330,7 @@
         <v>325</v>
       </c>
       <c r="U229" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V229" t="n">
         <v>54.81139</v>
@@ -16398,7 +16398,7 @@
         <v>325</v>
       </c>
       <c r="U230" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V230" t="n">
         <v>54.8945</v>
@@ -16466,7 +16466,7 @@
         <v>325</v>
       </c>
       <c r="U231" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V231" t="n">
         <v>54.96533</v>
@@ -16538,7 +16538,7 @@
         <v>325</v>
       </c>
       <c r="U232" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V232" t="n">
         <v>54.81086</v>
@@ -16610,7 +16610,7 @@
         <v>325</v>
       </c>
       <c r="U233" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V233" t="n">
         <v>54.84859</v>
@@ -16682,7 +16682,7 @@
         <v>325</v>
       </c>
       <c r="U234" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V234" t="n">
         <v>54.96403</v>
@@ -16750,7 +16750,7 @@
         <v>325</v>
       </c>
       <c r="U235" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V235" t="n">
         <v>54.97009</v>
@@ -16822,7 +16822,7 @@
         <v>325</v>
       </c>
       <c r="U236" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V236" t="n">
         <v>54.95694</v>
@@ -16894,7 +16894,7 @@
         <v>325</v>
       </c>
       <c r="U237" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V237" t="n">
         <v>54.82801</v>
@@ -16966,7 +16966,7 @@
         <v>325</v>
       </c>
       <c r="U238" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V238" t="n">
         <v>54.83869</v>
@@ -17034,7 +17034,7 @@
         <v>325</v>
       </c>
       <c r="U239" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V239" t="n">
         <v>54.79462</v>
@@ -17102,7 +17102,7 @@
         <v>325</v>
       </c>
       <c r="U240" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V240" t="n">
         <v>54.80039</v>
@@ -17170,7 +17170,7 @@
         <v>325</v>
       </c>
       <c r="U241" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V241" t="n">
         <v>54.83332</v>
@@ -17238,7 +17238,7 @@
         <v>325</v>
       </c>
       <c r="U242" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V242" t="n">
         <v>54.82853</v>
@@ -17306,7 +17306,7 @@
         <v>325</v>
       </c>
       <c r="U243" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V243" t="n">
         <v>54.82814</v>
@@ -17374,7 +17374,7 @@
         <v>325</v>
       </c>
       <c r="U244" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V244" t="n">
         <v>54.83819</v>
@@ -17442,7 +17442,7 @@
         <v>325</v>
       </c>
       <c r="U245" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V245" t="n">
         <v>54.84844</v>
@@ -17510,7 +17510,7 @@
         <v>325</v>
       </c>
       <c r="U246" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V246" t="n">
         <v>54.8347</v>
@@ -17578,7 +17578,7 @@
         <v>325</v>
       </c>
       <c r="U247" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V247" t="n">
         <v>54.85312</v>
@@ -17646,7 +17646,7 @@
         <v>325</v>
       </c>
       <c r="U248" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V248" t="n">
         <v>54.88663</v>
@@ -17714,7 +17714,7 @@
         <v>325</v>
       </c>
       <c r="U249" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V249" t="n">
         <v>54.86817</v>
@@ -17782,7 +17782,7 @@
         <v>325</v>
       </c>
       <c r="U250" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V250" t="n">
         <v>54.88674</v>
@@ -17850,7 +17850,7 @@
         <v>325</v>
       </c>
       <c r="U251" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V251" t="n">
         <v>54.87367</v>
@@ -17918,7 +17918,7 @@
         <v>325</v>
       </c>
       <c r="U252" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V252" t="n">
         <v>54.90649</v>
@@ -17986,7 +17986,7 @@
         <v>325</v>
       </c>
       <c r="U253" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V253" t="n">
         <v>54.90732</v>
@@ -18054,7 +18054,7 @@
         <v>325</v>
       </c>
       <c r="U254" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V254" t="n">
         <v>54.89657</v>
@@ -18122,7 +18122,7 @@
         <v>325</v>
       </c>
       <c r="U255" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V255" t="n">
         <v>54.91334</v>
@@ -18190,7 +18190,7 @@
         <v>325</v>
       </c>
       <c r="U256" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V256" t="n">
         <v>54.89171</v>
@@ -18258,7 +18258,7 @@
         <v>325</v>
       </c>
       <c r="U257" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V257" t="n">
         <v>54.88884</v>
@@ -18326,7 +18326,7 @@
         <v>325</v>
       </c>
       <c r="U258" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V258" t="n">
         <v>54.92746</v>
@@ -18394,7 +18394,7 @@
         <v>325</v>
       </c>
       <c r="U259" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V259" t="n">
         <v>54.95041</v>
@@ -18462,7 +18462,7 @@
         <v>325</v>
       </c>
       <c r="U260" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V260" t="n">
         <v>54.95193</v>
@@ -18530,7 +18530,7 @@
         <v>325</v>
       </c>
       <c r="U261" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V261" t="n">
         <v>54.98293</v>
@@ -18598,7 +18598,7 @@
         <v>250</v>
       </c>
       <c r="U262" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V262" t="n">
         <v>54.99823</v>
@@ -18666,7 +18666,7 @@
         <v>250</v>
       </c>
       <c r="U263" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V263" t="n">
         <v>54.99467</v>
@@ -18734,7 +18734,7 @@
         <v>325</v>
       </c>
       <c r="U264" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V264" t="n">
         <v>54.80005</v>
@@ -18802,7 +18802,7 @@
         <v>325</v>
       </c>
       <c r="U265" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V265" t="n">
         <v>54.79166</v>
@@ -18870,7 +18870,7 @@
         <v>325</v>
       </c>
       <c r="U266" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V266" t="n">
         <v>54.75892</v>
@@ -18938,7 +18938,7 @@
         <v>325</v>
       </c>
       <c r="U267" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V267" t="n">
         <v>54.88526</v>
@@ -19006,7 +19006,7 @@
         <v>325</v>
       </c>
       <c r="U268" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V268" t="n">
         <v>54.86337</v>
@@ -19074,7 +19074,7 @@
         <v>325</v>
       </c>
       <c r="U269" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V269" t="n">
         <v>54.80493</v>
@@ -19142,7 +19142,7 @@
         <v>325</v>
       </c>
       <c r="U270" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V270" t="n">
         <v>54.86705</v>
@@ -19210,7 +19210,7 @@
         <v>325</v>
       </c>
       <c r="U271" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V271" t="n">
         <v>54.85841</v>
@@ -19278,7 +19278,7 @@
         <v>325</v>
       </c>
       <c r="U272" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V272" t="n">
         <v>54.83623</v>
@@ -19346,7 +19346,7 @@
         <v>325</v>
       </c>
       <c r="U273" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V273" t="n">
         <v>54.24831</v>
@@ -19414,7 +19414,7 @@
         <v>325</v>
       </c>
       <c r="U274" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V274" t="n">
         <v>54.17246</v>
@@ -19482,7 +19482,7 @@
         <v>325</v>
       </c>
       <c r="U275" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V275" t="n">
         <v>54.07299</v>
@@ -19550,7 +19550,7 @@
         <v>325</v>
       </c>
       <c r="U276" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V276" t="n">
         <v>54.1302</v>
@@ -19618,7 +19618,7 @@
         <v>325</v>
       </c>
       <c r="U277" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V277" t="n">
         <v>54.16423</v>
@@ -19686,7 +19686,7 @@
         <v>325</v>
       </c>
       <c r="U278" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V278" t="n">
         <v>54.19639</v>
@@ -19754,7 +19754,7 @@
         <v>325</v>
       </c>
       <c r="U279" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V279" t="n">
         <v>54.20378</v>
@@ -19822,7 +19822,7 @@
         <v>325</v>
       </c>
       <c r="U280" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V280" t="n">
         <v>54.20174</v>
@@ -19890,7 +19890,7 @@
         <v>325</v>
       </c>
       <c r="U281" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V281" t="n">
         <v>54.23093</v>
@@ -19958,7 +19958,7 @@
         <v>325</v>
       </c>
       <c r="U282" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V282" t="n">
         <v>54.20838</v>
@@ -20026,7 +20026,7 @@
         <v>325</v>
       </c>
       <c r="U283" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V283" t="n">
         <v>54.1236</v>
@@ -20094,7 +20094,7 @@
         <v>250</v>
       </c>
       <c r="U284" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V284" t="n">
         <v>54.08077</v>
@@ -20162,7 +20162,7 @@
         <v>325</v>
       </c>
       <c r="U285" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V285" t="n">
         <v>54.18352</v>
@@ -20230,7 +20230,7 @@
         <v>325</v>
       </c>
       <c r="U286" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V286" t="n">
         <v>54.22162</v>
@@ -20298,7 +20298,7 @@
         <v>325</v>
       </c>
       <c r="U287" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V287" t="n">
         <v>54.02005</v>
@@ -20366,7 +20366,7 @@
         <v>325</v>
       </c>
       <c r="U288" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V288" t="n">
         <v>54.10074</v>
@@ -20434,7 +20434,7 @@
         <v>250</v>
       </c>
       <c r="U289" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V289" t="n">
         <v>54.07516</v>
@@ -20502,7 +20502,7 @@
         <v>325</v>
       </c>
       <c r="U290" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V290" t="n">
         <v>54.19246</v>
@@ -20570,7 +20570,7 @@
         <v>325</v>
       </c>
       <c r="U291" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V291" t="n">
         <v>54.14527</v>
@@ -20642,7 +20642,7 @@
         <v>325</v>
       </c>
       <c r="U292" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V292" t="n">
         <v>54.21839</v>
@@ -20710,7 +20710,7 @@
         <v>325</v>
       </c>
       <c r="U293" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V293" t="n">
         <v>54.23618</v>
@@ -20778,7 +20778,7 @@
         <v>325</v>
       </c>
       <c r="U294" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V294" t="n">
         <v>54.23455</v>
@@ -20846,7 +20846,7 @@
         <v>325</v>
       </c>
       <c r="U295" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V295" t="n">
         <v>54.19893</v>
@@ -20914,7 +20914,7 @@
         <v>325</v>
       </c>
       <c r="U296" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V296" t="n">
         <v>54.167</v>
@@ -20982,7 +20982,7 @@
         <v>325</v>
       </c>
       <c r="U297" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V297" t="n">
         <v>54.08077</v>
@@ -21050,7 +21050,7 @@
         <v>325</v>
       </c>
       <c r="U298" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V298" t="n">
         <v>54.10786</v>
@@ -21118,7 +21118,7 @@
         <v>325</v>
       </c>
       <c r="U299" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V299" t="n">
         <v>54.08988</v>
@@ -21186,7 +21186,7 @@
         <v>325</v>
       </c>
       <c r="U300" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V300" t="n">
         <v>54.49757</v>
@@ -21254,7 +21254,7 @@
         <v>325</v>
       </c>
       <c r="U301" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V301" t="n">
         <v>54.48828</v>
@@ -21322,7 +21322,7 @@
         <v>325</v>
       </c>
       <c r="U302" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V302" t="n">
         <v>54.47165</v>
@@ -21390,7 +21390,7 @@
         <v>325</v>
       </c>
       <c r="U303" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V303" t="n">
         <v>54.48665</v>
@@ -21458,7 +21458,7 @@
         <v>325</v>
       </c>
       <c r="U304" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V304" t="n">
         <v>54.49479</v>
@@ -21526,7 +21526,7 @@
         <v>325</v>
       </c>
       <c r="U305" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V305" t="n">
         <v>54.44989</v>
@@ -21594,7 +21594,7 @@
         <v>325</v>
       </c>
       <c r="U306" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V306" t="n">
         <v>54.44656</v>
@@ -21662,7 +21662,7 @@
         <v>325</v>
       </c>
       <c r="U307" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V307" t="n">
         <v>54.43649</v>
@@ -21730,7 +21730,7 @@
         <v>325</v>
       </c>
       <c r="U308" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V308" t="n">
         <v>54.36122</v>
@@ -21798,7 +21798,7 @@
         <v>325</v>
       </c>
       <c r="U309" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V309" t="n">
         <v>54.32282</v>
@@ -21866,7 +21866,7 @@
         <v>325</v>
       </c>
       <c r="U310" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V310" t="n">
         <v>54.2696</v>
@@ -21934,7 +21934,7 @@
         <v>325</v>
       </c>
       <c r="U311" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V311" t="n">
         <v>54.28794</v>
@@ -22002,7 +22002,7 @@
         <v>325</v>
       </c>
       <c r="U312" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V312" t="n">
         <v>54.27045</v>
@@ -22070,7 +22070,7 @@
         <v>325</v>
       </c>
       <c r="U313" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V313" t="n">
         <v>54.38406</v>
@@ -22138,7 +22138,7 @@
         <v>325</v>
       </c>
       <c r="U314" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V314" t="n">
         <v>54.37242</v>
@@ -22206,7 +22206,7 @@
         <v>325</v>
       </c>
       <c r="U315" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V315" t="n">
         <v>54.38089</v>
@@ -22274,7 +22274,7 @@
         <v>325</v>
       </c>
       <c r="U316" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V316" t="n">
         <v>54.38229</v>
@@ -22342,7 +22342,7 @@
         <v>325</v>
       </c>
       <c r="U317" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V317" t="n">
         <v>54.38048</v>
@@ -22410,7 +22410,7 @@
         <v>325</v>
       </c>
       <c r="U318" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V318" t="n">
         <v>54.38989</v>
@@ -22478,7 +22478,7 @@
         <v>325</v>
       </c>
       <c r="U319" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V319" t="n">
         <v>54.39175</v>
@@ -22546,7 +22546,7 @@
         <v>325</v>
       </c>
       <c r="U320" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V320" t="n">
         <v>54.39078</v>
@@ -22614,7 +22614,7 @@
         <v>325</v>
       </c>
       <c r="U321" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V321" t="n">
         <v>54.40456</v>
@@ -22682,7 +22682,7 @@
         <v>325</v>
       </c>
       <c r="U322" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V322" t="n">
         <v>54.40028</v>
@@ -22750,7 +22750,7 @@
         <v>325</v>
       </c>
       <c r="U323" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V323" t="n">
         <v>54.40564</v>
@@ -22818,7 +22818,7 @@
         <v>325</v>
       </c>
       <c r="U324" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V324" t="n">
         <v>54.40798</v>
@@ -22886,7 +22886,7 @@
         <v>325</v>
       </c>
       <c r="U325" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V325" t="n">
         <v>54.41185</v>
@@ -22954,7 +22954,7 @@
         <v>325</v>
       </c>
       <c r="U326" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V326" t="n">
         <v>54.41279</v>
@@ -23022,7 +23022,7 @@
         <v>325</v>
       </c>
       <c r="U327" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V327" t="n">
         <v>54.41634</v>
@@ -23090,7 +23090,7 @@
         <v>325</v>
       </c>
       <c r="U328" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V328" t="n">
         <v>54.42171</v>
@@ -23158,7 +23158,7 @@
         <v>325</v>
       </c>
       <c r="U329" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V329" t="n">
         <v>54.43025</v>
@@ -23226,7 +23226,7 @@
         <v>325</v>
       </c>
       <c r="U330" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V330" t="n">
         <v>54.4444</v>
@@ -23294,7 +23294,7 @@
         <v>325</v>
       </c>
       <c r="U331" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V331" t="n">
         <v>54.46056</v>
@@ -23362,7 +23362,7 @@
         <v>325</v>
       </c>
       <c r="U332" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V332" t="n">
         <v>54.4422</v>
@@ -23430,7 +23430,7 @@
         <v>325</v>
       </c>
       <c r="U333" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V333" t="n">
         <v>54.4108</v>
@@ -23498,7 +23498,7 @@
         <v>325</v>
       </c>
       <c r="U334" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V334" t="n">
         <v>54.43488</v>
@@ -23566,7 +23566,7 @@
         <v>325</v>
       </c>
       <c r="U335" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V335" t="n">
         <v>54.45411</v>
@@ -23634,7 +23634,7 @@
         <v>325</v>
       </c>
       <c r="U336" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V336" t="n">
         <v>54.46953</v>
@@ -23702,7 +23702,7 @@
         <v>325</v>
       </c>
       <c r="U337" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V337" t="n">
         <v>54.46112</v>
@@ -23770,7 +23770,7 @@
         <v>325</v>
       </c>
       <c r="U338" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V338" t="n">
         <v>54.4658</v>
@@ -23838,7 +23838,7 @@
         <v>325</v>
       </c>
       <c r="U339" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V339" t="n">
         <v>54.47577</v>
@@ -23906,7 +23906,7 @@
         <v>325</v>
       </c>
       <c r="U340" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V340" t="n">
         <v>54.4809</v>
@@ -23974,7 +23974,7 @@
         <v>325</v>
       </c>
       <c r="U341" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V341" t="n">
         <v>54.49743</v>
@@ -24042,7 +24042,7 @@
         <v>325</v>
       </c>
       <c r="U342" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V342" t="n">
         <v>54.4911</v>
@@ -24110,7 +24110,7 @@
         <v>325</v>
       </c>
       <c r="U343" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V343" t="n">
         <v>54.48089</v>
@@ -24178,7 +24178,7 @@
         <v>325</v>
       </c>
       <c r="U344" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V344" t="n">
         <v>54.49383</v>
@@ -24246,7 +24246,7 @@
         <v>325</v>
       </c>
       <c r="U345" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V345" t="n">
         <v>54.26004</v>
@@ -24314,7 +24314,7 @@
         <v>325</v>
       </c>
       <c r="U346" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V346" t="n">
         <v>54.32517</v>
@@ -24382,7 +24382,7 @@
         <v>325</v>
       </c>
       <c r="U347" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V347" t="n">
         <v>54.33793</v>
@@ -24450,7 +24450,7 @@
         <v>325</v>
       </c>
       <c r="U348" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V348" t="n">
         <v>54.4031</v>
@@ -24518,7 +24518,7 @@
         <v>325</v>
       </c>
       <c r="U349" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V349" t="n">
         <v>54.413</v>
@@ -24586,7 +24586,7 @@
         <v>325</v>
       </c>
       <c r="U350" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V350" t="n">
         <v>54.40993</v>
@@ -24654,7 +24654,7 @@
         <v>325</v>
       </c>
       <c r="U351" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V351" t="n">
         <v>54.41772</v>
@@ -24722,7 +24722,7 @@
         <v>325</v>
       </c>
       <c r="U352" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V352" t="n">
         <v>54.45965</v>
@@ -24790,7 +24790,7 @@
         <v>325</v>
       </c>
       <c r="U353" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V353" t="n">
         <v>54.48347</v>
@@ -24858,7 +24858,7 @@
         <v>325</v>
       </c>
       <c r="U354" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V354" t="n">
         <v>54.49776</v>
@@ -24926,7 +24926,7 @@
         <v>325</v>
       </c>
       <c r="U355" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V355" t="n">
         <v>54.45647</v>
@@ -24994,7 +24994,7 @@
         <v>325</v>
       </c>
       <c r="U356" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V356" t="n">
         <v>54.44469</v>
@@ -25062,7 +25062,7 @@
         <v>325</v>
       </c>
       <c r="U357" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V357" t="n">
         <v>54.4479</v>
@@ -25130,7 +25130,7 @@
         <v>325</v>
       </c>
       <c r="U358" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V358" t="n">
         <v>54.43159</v>
@@ -25198,7 +25198,7 @@
         <v>325</v>
       </c>
       <c r="U359" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V359" t="n">
         <v>54.47225</v>
@@ -25266,7 +25266,7 @@
         <v>325</v>
       </c>
       <c r="U360" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V360" t="n">
         <v>54.47347</v>
@@ -25334,7 +25334,7 @@
         <v>325</v>
       </c>
       <c r="U361" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V361" t="n">
         <v>54.46751</v>
@@ -25402,7 +25402,7 @@
         <v>325</v>
       </c>
       <c r="U362" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V362" t="n">
         <v>54.46336</v>
@@ -25470,7 +25470,7 @@
         <v>325</v>
       </c>
       <c r="U363" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V363" t="n">
         <v>54.45778</v>
@@ -25542,7 +25542,7 @@
         <v>325</v>
       </c>
       <c r="U364" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V364" t="n">
         <v>54.40333</v>
@@ -25614,7 +25614,7 @@
         <v>325</v>
       </c>
       <c r="U365" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V365" t="n">
         <v>54.48489</v>
@@ -25682,7 +25682,7 @@
         <v>325</v>
       </c>
       <c r="U366" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V366" t="n">
         <v>54.43179</v>
@@ -25754,7 +25754,7 @@
         <v>325</v>
       </c>
       <c r="U367" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V367" t="n">
         <v>56.92466</v>
@@ -25826,7 +25826,7 @@
         <v>325</v>
       </c>
       <c r="U368" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V368" t="n">
         <v>56.90917</v>
@@ -25898,7 +25898,7 @@
         <v>325</v>
       </c>
       <c r="U369" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V369" t="n">
         <v>56.87709</v>
@@ -25970,7 +25970,7 @@
         <v>325</v>
       </c>
       <c r="U370" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V370" t="n">
         <v>56.67204</v>
@@ -26042,7 +26042,7 @@
         <v>325</v>
       </c>
       <c r="U371" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V371" t="n">
         <v>56.59886</v>
@@ -26114,7 +26114,7 @@
         <v>325</v>
       </c>
       <c r="U372" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V372" t="n">
         <v>56.75025</v>
@@ -26186,7 +26186,7 @@
         <v>325</v>
       </c>
       <c r="U373" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V373" t="n">
         <v>56.67232</v>
@@ -26258,7 +26258,7 @@
         <v>325</v>
       </c>
       <c r="U374" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V374" t="n">
         <v>56.65024</v>
@@ -26330,7 +26330,7 @@
         <v>325</v>
       </c>
       <c r="U375" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V375" t="n">
         <v>56.69932</v>
@@ -26402,7 +26402,7 @@
         <v>325</v>
       </c>
       <c r="U376" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V376" t="n">
         <v>56.69275</v>
@@ -26474,7 +26474,7 @@
         <v>325</v>
       </c>
       <c r="U377" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V377" t="n">
         <v>56.65894</v>
@@ -26546,7 +26546,7 @@
         <v>325</v>
       </c>
       <c r="U378" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V378" t="n">
         <v>56.63339</v>
@@ -26618,7 +26618,7 @@
         <v>325</v>
       </c>
       <c r="U379" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V379" t="n">
         <v>56.74891</v>
@@ -26690,7 +26690,7 @@
         <v>325</v>
       </c>
       <c r="U380" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V380" t="n">
         <v>56.52942</v>
@@ -26762,7 +26762,7 @@
         <v>325</v>
       </c>
       <c r="U381" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V381" t="n">
         <v>56.50489</v>
@@ -26834,7 +26834,7 @@
         <v>325</v>
       </c>
       <c r="U382" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V382" t="n">
         <v>56.71741</v>
@@ -26906,7 +26906,7 @@
         <v>325</v>
       </c>
       <c r="U383" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V383" t="n">
         <v>56.69293</v>
@@ -26978,7 +26978,7 @@
         <v>325</v>
       </c>
       <c r="U384" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V384" t="n">
         <v>56.70755</v>
@@ -27050,7 +27050,7 @@
         <v>325</v>
       </c>
       <c r="U385" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V385" t="n">
         <v>56.65617</v>
@@ -27122,7 +27122,7 @@
         <v>325</v>
       </c>
       <c r="U386" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V386" t="n">
         <v>56.67107</v>
@@ -27194,7 +27194,7 @@
         <v>325</v>
       </c>
       <c r="U387" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V387" t="n">
         <v>56.73239</v>
@@ -27266,7 +27266,7 @@
         <v>325</v>
       </c>
       <c r="U388" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V388" t="n">
         <v>56.74349</v>
@@ -27338,7 +27338,7 @@
         <v>325</v>
       </c>
       <c r="U389" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V389" t="n">
         <v>56.88342</v>
@@ -27410,7 +27410,7 @@
         <v>325</v>
       </c>
       <c r="U390" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V390" t="n">
         <v>56.74754</v>
@@ -27482,7 +27482,7 @@
         <v>325</v>
       </c>
       <c r="U391" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V391" t="n">
         <v>56.68885</v>
@@ -27554,7 +27554,7 @@
         <v>325</v>
       </c>
       <c r="U392" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V392" t="n">
         <v>56.72121</v>
@@ -27626,7 +27626,7 @@
         <v>325</v>
       </c>
       <c r="U393" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V393" t="n">
         <v>56.74279</v>
@@ -27698,7 +27698,7 @@
         <v>325</v>
       </c>
       <c r="U394" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V394" t="n">
         <v>56.66587</v>
@@ -27770,7 +27770,7 @@
         <v>325</v>
       </c>
       <c r="U395" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V395" t="n">
         <v>56.72065</v>
@@ -27842,7 +27842,7 @@
         <v>325</v>
       </c>
       <c r="U396" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V396" t="n">
         <v>56.51332</v>
@@ -27914,7 +27914,7 @@
         <v>325</v>
       </c>
       <c r="U397" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V397" t="n">
         <v>56.65137</v>
@@ -27986,7 +27986,7 @@
         <v>325</v>
       </c>
       <c r="U398" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V398" t="n">
         <v>56.57146</v>
@@ -28058,7 +28058,7 @@
         <v>325</v>
       </c>
       <c r="U399" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V399" t="n">
         <v>56.6069</v>
@@ -28130,7 +28130,7 @@
         <v>325</v>
       </c>
       <c r="U400" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V400" t="n">
         <v>56.74673</v>
@@ -28202,7 +28202,7 @@
         <v>325</v>
       </c>
       <c r="U401" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V401" t="n">
         <v>56.72247</v>
@@ -28274,7 +28274,7 @@
         <v>325</v>
       </c>
       <c r="U402" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V402" t="n">
         <v>56.72536</v>
@@ -28342,7 +28342,7 @@
         <v>325</v>
       </c>
       <c r="U403" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V403" t="n">
         <v>56.74162</v>
@@ -28414,7 +28414,7 @@
         <v>325</v>
       </c>
       <c r="U404" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V404" t="n">
         <v>56.63381</v>
@@ -28486,7 +28486,7 @@
         <v>325</v>
       </c>
       <c r="U405" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V405" t="n">
         <v>56.6452</v>
@@ -28558,7 +28558,7 @@
         <v>325</v>
       </c>
       <c r="U406" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V406" t="n">
         <v>56.6469</v>
@@ -28630,7 +28630,7 @@
         <v>325</v>
       </c>
       <c r="U407" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V407" t="n">
         <v>56.65702</v>
@@ -28702,7 +28702,7 @@
         <v>325</v>
       </c>
       <c r="U408" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V408" t="n">
         <v>56.66788</v>
@@ -28774,7 +28774,7 @@
         <v>325</v>
       </c>
       <c r="U409" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V409" t="n">
         <v>56.64847</v>
@@ -28846,7 +28846,7 @@
         <v>325</v>
       </c>
       <c r="U410" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V410" t="n">
         <v>56.70287</v>
@@ -28918,7 +28918,7 @@
         <v>325</v>
       </c>
       <c r="U411" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V411" t="n">
         <v>56.62324</v>
@@ -28990,7 +28990,7 @@
         <v>325</v>
       </c>
       <c r="U412" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V412" t="n">
         <v>56.60517</v>
@@ -29062,7 +29062,7 @@
         <v>325</v>
       </c>
       <c r="U413" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V413" t="n">
         <v>56.61671</v>
@@ -29134,7 +29134,7 @@
         <v>325</v>
       </c>
       <c r="U414" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V414" t="n">
         <v>56.5973</v>
@@ -29206,7 +29206,7 @@
         <v>325</v>
       </c>
       <c r="U415" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V415" t="n">
         <v>56.63791</v>
@@ -29278,7 +29278,7 @@
         <v>325</v>
       </c>
       <c r="U416" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V416" t="n">
         <v>56.66898</v>
@@ -29350,7 +29350,7 @@
         <v>325</v>
       </c>
       <c r="U417" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V417" t="n">
         <v>56.59251</v>
@@ -29422,7 +29422,7 @@
         <v>325</v>
       </c>
       <c r="U418" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V418" t="n">
         <v>56.61434</v>
@@ -29494,7 +29494,7 @@
         <v>325</v>
       </c>
       <c r="U419" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V419" t="n">
         <v>56.61785</v>
@@ -29566,7 +29566,7 @@
         <v>325</v>
       </c>
       <c r="U420" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V420" t="n">
         <v>56.60929</v>
@@ -29638,7 +29638,7 @@
         <v>325</v>
       </c>
       <c r="U421" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V421" t="n">
         <v>56.63907</v>
@@ -29710,7 +29710,7 @@
         <v>325</v>
       </c>
       <c r="U422" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V422" t="n">
         <v>56.63492</v>
@@ -29782,7 +29782,7 @@
         <v>325</v>
       </c>
       <c r="U423" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V423" t="n">
         <v>56.64648</v>
@@ -29854,7 +29854,7 @@
         <v>325</v>
       </c>
       <c r="U424" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V424" t="n">
         <v>56.63315</v>
@@ -29926,7 +29926,7 @@
         <v>325</v>
       </c>
       <c r="U425" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V425" t="n">
         <v>56.6058</v>
@@ -29998,7 +29998,7 @@
         <v>325</v>
       </c>
       <c r="U426" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V426" t="n">
         <v>56.58475</v>
@@ -30070,7 +30070,7 @@
         <v>325</v>
       </c>
       <c r="U427" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V427" t="n">
         <v>56.58307</v>
@@ -30142,7 +30142,7 @@
         <v>325</v>
       </c>
       <c r="U428" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V428" t="n">
         <v>56.58355</v>
@@ -30214,7 +30214,7 @@
         <v>325</v>
       </c>
       <c r="U429" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V429" t="n">
         <v>56.53385</v>
@@ -30286,7 +30286,7 @@
         <v>325</v>
       </c>
       <c r="U430" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V430" t="n">
         <v>56.55746</v>
@@ -30358,7 +30358,7 @@
         <v>325</v>
       </c>
       <c r="U431" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V431" t="n">
         <v>56.5876</v>
@@ -30430,7 +30430,7 @@
         <v>325</v>
       </c>
       <c r="U432" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V432" t="n">
         <v>56.6898</v>
@@ -30502,7 +30502,7 @@
         <v>325</v>
       </c>
       <c r="U433" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V433" t="n">
         <v>56.68122</v>
@@ -30574,7 +30574,7 @@
         <v>325</v>
       </c>
       <c r="U434" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V434" t="n">
         <v>56.71031</v>
@@ -30646,7 +30646,7 @@
         <v>325</v>
       </c>
       <c r="U435" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V435" t="n">
         <v>56.59804</v>
@@ -30718,7 +30718,7 @@
         <v>325</v>
       </c>
       <c r="U436" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V436" t="n">
         <v>56.54108</v>
@@ -30790,7 +30790,7 @@
         <v>325</v>
       </c>
       <c r="U437" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V437" t="n">
         <v>56.51586</v>
@@ -30862,7 +30862,7 @@
         <v>325</v>
       </c>
       <c r="U438" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V438" t="n">
         <v>56.51936</v>
@@ -30934,7 +30934,7 @@
         <v>325</v>
       </c>
       <c r="U439" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V439" t="n">
         <v>56.52909</v>
@@ -31006,7 +31006,7 @@
         <v>325</v>
       </c>
       <c r="U440" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V440" t="n">
         <v>56.5297</v>
@@ -31078,7 +31078,7 @@
         <v>325</v>
       </c>
       <c r="U441" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V441" t="n">
         <v>56.54708</v>
@@ -31150,7 +31150,7 @@
         <v>325</v>
       </c>
       <c r="U442" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V442" t="n">
         <v>56.58807</v>
@@ -31222,7 +31222,7 @@
         <v>325</v>
       </c>
       <c r="U443" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V443" t="n">
         <v>56.55273</v>
@@ -31294,7 +31294,7 @@
         <v>325</v>
       </c>
       <c r="U444" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V444" t="n">
         <v>56.53045</v>
@@ -31366,7 +31366,7 @@
         <v>325</v>
       </c>
       <c r="U445" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V445" t="n">
         <v>56.51738</v>
@@ -31438,7 +31438,7 @@
         <v>325</v>
       </c>
       <c r="U446" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V446" t="n">
         <v>56.53917</v>
@@ -31510,7 +31510,7 @@
         <v>325</v>
       </c>
       <c r="U447" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V447" t="n">
         <v>56.85355</v>
@@ -31582,7 +31582,7 @@
         <v>325</v>
       </c>
       <c r="U448" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V448" t="n">
         <v>56.84293</v>
@@ -31654,7 +31654,7 @@
         <v>325</v>
       </c>
       <c r="U449" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V449" t="n">
         <v>56.82041</v>
@@ -31726,7 +31726,7 @@
         <v>300</v>
       </c>
       <c r="U450" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V450" t="n">
         <v>56.8319</v>
@@ -31798,7 +31798,7 @@
         <v>325</v>
       </c>
       <c r="U451" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V451" t="n">
         <v>56.83195</v>
@@ -31870,7 +31870,7 @@
         <v>325</v>
       </c>
       <c r="U452" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V452" t="n">
         <v>56.83087</v>
@@ -31942,7 +31942,7 @@
         <v>325</v>
       </c>
       <c r="U453" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V453" t="n">
         <v>56.81957</v>
@@ -32014,7 +32014,7 @@
         <v>325</v>
       </c>
       <c r="U454" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V454" t="n">
         <v>56.75838</v>
@@ -32086,7 +32086,7 @@
         <v>325</v>
       </c>
       <c r="U455" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V455" t="n">
         <v>56.84701</v>
@@ -32158,7 +32158,7 @@
         <v>325</v>
       </c>
       <c r="U456" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V456" t="n">
         <v>56.87193</v>
@@ -32230,7 +32230,7 @@
         <v>325</v>
       </c>
       <c r="U457" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V457" t="n">
         <v>56.86168</v>
@@ -32302,7 +32302,7 @@
         <v>325</v>
       </c>
       <c r="U458" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V458" t="n">
         <v>56.79595</v>
@@ -32374,7 +32374,7 @@
         <v>325</v>
       </c>
       <c r="U459" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V459" t="n">
         <v>56.78585</v>
@@ -32446,7 +32446,7 @@
         <v>250</v>
       </c>
       <c r="U460" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V460" t="n">
         <v>56.78592</v>
@@ -32518,7 +32518,7 @@
         <v>325</v>
       </c>
       <c r="U461" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V461" t="n">
         <v>56.76943</v>
@@ -32590,7 +32590,7 @@
         <v>325</v>
       </c>
       <c r="U462" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V462" t="n">
         <v>56.82774</v>
@@ -32662,7 +32662,7 @@
         <v>325</v>
       </c>
       <c r="U463" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V463" t="n">
         <v>56.90065</v>
@@ -32730,7 +32730,7 @@
         <v>325</v>
       </c>
       <c r="U464" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V464" t="n">
         <v>56.85992</v>
@@ -32802,7 +32802,7 @@
         <v>325</v>
       </c>
       <c r="U465" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V465" t="n">
         <v>56.75649</v>
@@ -32874,7 +32874,7 @@
         <v>300</v>
       </c>
       <c r="U466" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V466" t="n">
         <v>56.82325</v>
@@ -32946,7 +32946,7 @@
         <v>325</v>
       </c>
       <c r="U467" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V467" t="n">
         <v>56.82261</v>
@@ -33018,7 +33018,7 @@
         <v>325</v>
       </c>
       <c r="U468" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V468" t="n">
         <v>56.83066</v>
@@ -33090,7 +33090,7 @@
         <v>325</v>
       </c>
       <c r="U469" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V469" t="n">
         <v>56.7672</v>
@@ -33158,7 +33158,7 @@
         <v>325</v>
       </c>
       <c r="U470" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V470" t="n">
         <v>55.08203</v>
@@ -33226,7 +33226,7 @@
         <v>325</v>
       </c>
       <c r="U471" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V471" t="n">
         <v>55.09212</v>
@@ -33294,7 +33294,7 @@
         <v>325</v>
       </c>
       <c r="U472" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V472" t="n">
         <v>55.10755</v>
@@ -33362,7 +33362,7 @@
         <v>325</v>
       </c>
       <c r="U473" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V473" t="n">
         <v>55.12438</v>
@@ -33430,7 +33430,7 @@
         <v>325</v>
       </c>
       <c r="U474" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V474" t="n">
         <v>55.13411</v>
@@ -33498,7 +33498,7 @@
         <v>325</v>
       </c>
       <c r="U475" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V475" t="n">
         <v>55.03986</v>
@@ -33566,7 +33566,7 @@
         <v>325</v>
       </c>
       <c r="U476" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V476" t="n">
         <v>55.05869</v>
@@ -33634,7 +33634,7 @@
         <v>325</v>
       </c>
       <c r="U477" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V477" t="n">
         <v>55.07593</v>
@@ -33702,7 +33702,7 @@
         <v>325</v>
       </c>
       <c r="U478" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V478" t="n">
         <v>55.13581</v>
@@ -33770,7 +33770,7 @@
         <v>325</v>
       </c>
       <c r="U479" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V479" t="n">
         <v>55.02194</v>
@@ -33842,7 +33842,7 @@
         <v>325</v>
       </c>
       <c r="U480" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V480" t="n">
         <v>55.16003</v>
@@ -33910,7 +33910,7 @@
         <v>250</v>
       </c>
       <c r="U481" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V481" t="n">
         <v>55.0058</v>
@@ -33978,7 +33978,7 @@
         <v>325</v>
       </c>
       <c r="U482" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V482" t="n">
         <v>55.016</v>
@@ -34046,7 +34046,7 @@
         <v>325</v>
       </c>
       <c r="U483" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V483" t="n">
         <v>55.0172</v>
@@ -34114,7 +34114,7 @@
         <v>325</v>
       </c>
       <c r="U484" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V484" t="n">
         <v>55.01415</v>
@@ -34182,7 +34182,7 @@
         <v>325</v>
       </c>
       <c r="U485" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V485" t="n">
         <v>55.02528</v>
@@ -34250,7 +34250,7 @@
         <v>325</v>
       </c>
       <c r="U486" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V486" t="n">
         <v>55.1045</v>
@@ -34318,7 +34318,7 @@
         <v>325</v>
       </c>
       <c r="U487" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V487" t="n">
         <v>55.16952</v>
@@ -34386,7 +34386,7 @@
         <v>325</v>
       </c>
       <c r="U488" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V488" t="n">
         <v>55.14566</v>
@@ -34454,7 +34454,7 @@
         <v>325</v>
       </c>
       <c r="U489" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V489" t="n">
         <v>55.14897</v>
@@ -34522,7 +34522,7 @@
         <v>325</v>
       </c>
       <c r="U490" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V490" t="n">
         <v>55.18003</v>
@@ -34590,7 +34590,7 @@
         <v>325</v>
       </c>
       <c r="U491" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V491" t="n">
         <v>55.24698</v>
@@ -34658,7 +34658,7 @@
         <v>325</v>
       </c>
       <c r="U492" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V492" t="n">
         <v>55.2292</v>
@@ -34726,7 +34726,7 @@
         <v>325</v>
       </c>
       <c r="U493" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V493" t="n">
         <v>55.21053</v>
@@ -34794,7 +34794,7 @@
         <v>325</v>
       </c>
       <c r="U494" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V494" t="n">
         <v>55.20109</v>
@@ -34862,7 +34862,7 @@
         <v>325</v>
       </c>
       <c r="U495" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V495" t="n">
         <v>55.2186</v>
@@ -34930,7 +34930,7 @@
         <v>325</v>
       </c>
       <c r="U496" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V496" t="n">
         <v>55.23123</v>
@@ -34998,7 +34998,7 @@
         <v>325</v>
       </c>
       <c r="U497" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V497" t="n">
         <v>55.06122</v>
@@ -35066,7 +35066,7 @@
         <v>325</v>
       </c>
       <c r="U498" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V498" t="n">
         <v>55.07226</v>
@@ -35134,7 +35134,7 @@
         <v>325</v>
       </c>
       <c r="U499" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V499" t="n">
         <v>55.07466</v>
@@ -35202,7 +35202,7 @@
         <v>325</v>
       </c>
       <c r="U500" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V500" t="n">
         <v>55.07645</v>
@@ -35270,7 +35270,7 @@
         <v>325</v>
       </c>
       <c r="U501" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V501" t="n">
         <v>55.07576</v>
@@ -35338,7 +35338,7 @@
         <v>325</v>
       </c>
       <c r="U502" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V502" t="n">
         <v>55.06628</v>
@@ -35406,7 +35406,7 @@
         <v>325</v>
       </c>
       <c r="U503" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V503" t="n">
         <v>55.0702</v>
@@ -35474,7 +35474,7 @@
         <v>325</v>
       </c>
       <c r="U504" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V504" t="n">
         <v>55.06977</v>
@@ -35542,7 +35542,7 @@
         <v>325</v>
       </c>
       <c r="U505" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V505" t="n">
         <v>55.058</v>
@@ -35610,7 +35610,7 @@
         <v>325</v>
       </c>
       <c r="U506" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V506" t="n">
         <v>55.07416</v>
@@ -35678,7 +35678,7 @@
         <v>325</v>
       </c>
       <c r="U507" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V507" t="n">
         <v>55.06214</v>
@@ -35746,7 +35746,7 @@
         <v>325</v>
       </c>
       <c r="U508" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V508" t="n">
         <v>55.06078</v>
@@ -35814,7 +35814,7 @@
         <v>325</v>
       </c>
       <c r="U509" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V509" t="n">
         <v>55.03279</v>
@@ -35882,7 +35882,7 @@
         <v>325</v>
       </c>
       <c r="U510" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V510" t="n">
         <v>55.04325</v>
@@ -35950,7 +35950,7 @@
         <v>325</v>
       </c>
       <c r="U511" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V511" t="n">
         <v>55.0414</v>
@@ -36018,7 +36018,7 @@
         <v>325</v>
       </c>
       <c r="U512" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V512" t="n">
         <v>55.04721</v>
@@ -36086,7 +36086,7 @@
         <v>325</v>
       </c>
       <c r="U513" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V513" t="n">
         <v>55.03949</v>
@@ -36154,7 +36154,7 @@
         <v>325</v>
       </c>
       <c r="U514" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V514" t="n">
         <v>55.04104</v>
@@ -36222,7 +36222,7 @@
         <v>325</v>
       </c>
       <c r="U515" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V515" t="n">
         <v>55.04067</v>
@@ -36290,7 +36290,7 @@
         <v>325</v>
       </c>
       <c r="U516" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V516" t="n">
         <v>55.04035</v>
@@ -36358,7 +36358,7 @@
         <v>325</v>
       </c>
       <c r="U517" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V517" t="n">
         <v>55.04554</v>
@@ -36426,7 +36426,7 @@
         <v>325</v>
       </c>
       <c r="U518" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V518" t="n">
         <v>55.03851</v>
@@ -36494,7 +36494,7 @@
         <v>325</v>
       </c>
       <c r="U519" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V519" t="n">
         <v>55.08205</v>
@@ -36562,7 +36562,7 @@
         <v>325</v>
       </c>
       <c r="U520" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V520" t="n">
         <v>55.08034</v>
@@ -36630,7 +36630,7 @@
         <v>325</v>
       </c>
       <c r="U521" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V521" t="n">
         <v>55.07966</v>
@@ -36698,7 +36698,7 @@
         <v>325</v>
       </c>
       <c r="U522" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V522" t="n">
         <v>55.0654</v>
@@ -36766,7 +36766,7 @@
         <v>325</v>
       </c>
       <c r="U523" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V523" t="n">
         <v>55.07866</v>
@@ -36834,7 +36834,7 @@
         <v>325</v>
       </c>
       <c r="U524" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V524" t="n">
         <v>55.07365</v>
@@ -36902,7 +36902,7 @@
         <v>325</v>
       </c>
       <c r="U525" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V525" t="n">
         <v>55.07132</v>
@@ -36970,7 +36970,7 @@
         <v>325</v>
       </c>
       <c r="U526" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V526" t="n">
         <v>55.01309</v>
@@ -37042,7 +37042,7 @@
         <v>250</v>
       </c>
       <c r="U527" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V527" t="n">
         <v>55.005</v>
@@ -37110,7 +37110,7 @@
         <v>325</v>
       </c>
       <c r="U528" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V528" t="n">
         <v>55.01924</v>
@@ -37178,7 +37178,7 @@
         <v>325</v>
       </c>
       <c r="U529" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V529" t="n">
         <v>55.07307</v>
@@ -37246,7 +37246,7 @@
         <v>325</v>
       </c>
       <c r="U530" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V530" t="n">
         <v>55.02119</v>
@@ -37314,7 +37314,7 @@
         <v>325</v>
       </c>
       <c r="U531" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V531" t="n">
         <v>55.0227</v>
@@ -37382,7 +37382,7 @@
         <v>325</v>
       </c>
       <c r="U532" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V532" t="n">
         <v>55.09552</v>
@@ -37450,7 +37450,7 @@
         <v>325</v>
       </c>
       <c r="U533" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V533" t="n">
         <v>55.08722</v>
@@ -37518,7 +37518,7 @@
         <v>325</v>
       </c>
       <c r="U534" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V534" t="n">
         <v>55.08769</v>
@@ -37586,7 +37586,7 @@
         <v>325</v>
       </c>
       <c r="U535" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V535" t="n">
         <v>55.07207</v>
@@ -37654,7 +37654,7 @@
         <v>325</v>
       </c>
       <c r="U536" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V536" t="n">
         <v>55.01346</v>
@@ -37722,7 +37722,7 @@
         <v>325</v>
       </c>
       <c r="U537" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V537" t="n">
         <v>55.02672</v>
@@ -37790,7 +37790,7 @@
         <v>325</v>
       </c>
       <c r="U538" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V538" t="n">
         <v>55.01336</v>
@@ -37858,7 +37858,7 @@
         <v>325</v>
       </c>
       <c r="U539" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V539" t="n">
         <v>55.04402</v>
@@ -37926,7 +37926,7 @@
         <v>300</v>
       </c>
       <c r="U540" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V540" t="n">
         <v>55.01039</v>
@@ -37994,7 +37994,7 @@
         <v>250</v>
       </c>
       <c r="U541" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V541" t="n">
         <v>55.00738</v>
@@ -38066,7 +38066,7 @@
         <v>325</v>
       </c>
       <c r="U542" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V542" t="n">
         <v>55.22021</v>
@@ -38138,7 +38138,7 @@
         <v>325</v>
       </c>
       <c r="U543" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V543" t="n">
         <v>55.23395</v>
@@ -38206,7 +38206,7 @@
         <v>325</v>
       </c>
       <c r="U544" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V544" t="n">
         <v>55.47866</v>
@@ -38278,7 +38278,7 @@
         <v>325</v>
       </c>
       <c r="U545" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V545" t="n">
         <v>55.25994</v>
@@ -38350,7 +38350,7 @@
         <v>325</v>
       </c>
       <c r="U546" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V546" t="n">
         <v>55.27542</v>
@@ -38422,7 +38422,7 @@
         <v>325</v>
       </c>
       <c r="U547" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V547" t="n">
         <v>55.26034</v>
@@ -38490,7 +38490,7 @@
         <v>325</v>
       </c>
       <c r="U548" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V548" t="n">
         <v>55.52156</v>
@@ -38562,7 +38562,7 @@
         <v>325</v>
       </c>
       <c r="U549" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V549" t="n">
         <v>56.21673</v>
@@ -38634,7 +38634,7 @@
         <v>250</v>
       </c>
       <c r="U550" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V550" t="n">
         <v>56.00554</v>
@@ -38706,7 +38706,7 @@
         <v>300</v>
       </c>
       <c r="U551" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V551" t="n">
         <v>56.01037</v>
@@ -38778,7 +38778,7 @@
         <v>325</v>
       </c>
       <c r="U552" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V552" t="n">
         <v>56.08247</v>
@@ -38850,7 +38850,7 @@
         <v>325</v>
       </c>
       <c r="U553" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V553" t="n">
         <v>56.14132</v>
@@ -38922,7 +38922,7 @@
         <v>325</v>
       </c>
       <c r="U554" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V554" t="n">
         <v>56.15311</v>
@@ -38994,7 +38994,7 @@
         <v>325</v>
       </c>
       <c r="U555" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V555" t="n">
         <v>56.1524</v>
@@ -39066,7 +39066,7 @@
         <v>325</v>
       </c>
       <c r="U556" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V556" t="n">
         <v>56.06154</v>
@@ -39138,7 +39138,7 @@
         <v>300</v>
       </c>
       <c r="U557" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V557" t="n">
         <v>56.01382</v>
@@ -39210,7 +39210,7 @@
         <v>325</v>
       </c>
       <c r="U558" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V558" t="n">
         <v>56.02406</v>
@@ -39282,7 +39282,7 @@
         <v>325</v>
       </c>
       <c r="U559" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V559" t="n">
         <v>56.02505</v>
@@ -39354,7 +39354,7 @@
         <v>300</v>
       </c>
       <c r="U560" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V560" t="n">
         <v>56.02362</v>
@@ -39426,7 +39426,7 @@
         <v>325</v>
       </c>
       <c r="U561" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V561" t="n">
         <v>56.08482</v>
@@ -39498,7 +39498,7 @@
         <v>325</v>
       </c>
       <c r="U562" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V562" t="n">
         <v>56.13466</v>
@@ -39570,7 +39570,7 @@
         <v>325</v>
       </c>
       <c r="U563" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V563" t="n">
         <v>56.12978</v>
@@ -39642,7 +39642,7 @@
         <v>225</v>
       </c>
       <c r="U564" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V564" t="n">
         <v>56.13047</v>
@@ -39714,7 +39714,7 @@
         <v>325</v>
       </c>
       <c r="U565" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V565" t="n">
         <v>56.03945</v>
@@ -39786,7 +39786,7 @@
         <v>275</v>
       </c>
       <c r="U566" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V566" t="n">
         <v>56.22999</v>
@@ -39858,7 +39858,7 @@
         <v>325</v>
       </c>
       <c r="U567" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V567" t="n">
         <v>56.47681</v>
@@ -39930,7 +39930,7 @@
         <v>325</v>
       </c>
       <c r="U568" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V568" t="n">
         <v>56.44848</v>
@@ -40002,7 +40002,7 @@
         <v>325</v>
       </c>
       <c r="U569" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V569" t="n">
         <v>56.45173</v>

--- a/site/mb_leads.xlsx
+++ b/site/mb_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X211"/>
+  <dimension ref="A1:X209"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -14644,142 +14644,6 @@
       </c>
       <c r="X209" t="inlineStr"/>
     </row>
-    <row r="210">
-      <c r="A210" t="n">
-        <v>209</v>
-      </c>
-      <c r="B210" t="inlineStr">
-        <is>
-          <t>Anderson Lake Mine</t>
-        </is>
-      </c>
-      <c r="C210" t="inlineStr">
-        <is>
-          <t>MBMINE-Anderson Lake Mine</t>
-        </is>
-      </c>
-      <c r="D210" t="inlineStr"/>
-      <c r="E210" t="inlineStr"/>
-      <c r="F210" t="inlineStr">
-        <is>
-          <t>Other metallic</t>
-        </is>
-      </c>
-      <c r="G210" t="inlineStr">
-        <is>
-          <t>Cu, Zn, Au, Ag</t>
-        </is>
-      </c>
-      <c r="H210" t="inlineStr">
-        <is>
-          <t>Past Producer</t>
-        </is>
-      </c>
-      <c r="I210" t="b">
-        <v>0</v>
-      </c>
-      <c r="J210" t="b">
-        <v>0</v>
-      </c>
-      <c r="K210" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L210" t="inlineStr"/>
-      <c r="M210" t="inlineStr"/>
-      <c r="N210" t="inlineStr"/>
-      <c r="O210" t="n">
-        <v>0</v>
-      </c>
-      <c r="P210" t="inlineStr"/>
-      <c r="Q210" t="inlineStr"/>
-      <c r="R210" t="inlineStr"/>
-      <c r="S210" t="n">
-        <v>8</v>
-      </c>
-      <c r="T210" t="n">
-        <v>200</v>
-      </c>
-      <c r="U210" t="n">
-        <v>14</v>
-      </c>
-      <c r="V210" t="n">
-        <v>54.86069</v>
-      </c>
-      <c r="W210" t="n">
-        <v>-99.99409</v>
-      </c>
-      <c r="X210" t="inlineStr"/>
-    </row>
-    <row r="211">
-      <c r="A211" t="n">
-        <v>210</v>
-      </c>
-      <c r="B211" t="inlineStr">
-        <is>
-          <t>Gilbert Shaft</t>
-        </is>
-      </c>
-      <c r="C211" t="inlineStr">
-        <is>
-          <t>MBMINE-Gilbert Shaft</t>
-        </is>
-      </c>
-      <c r="D211" t="inlineStr"/>
-      <c r="E211" t="inlineStr"/>
-      <c r="F211" t="inlineStr">
-        <is>
-          <t>Other metallic</t>
-        </is>
-      </c>
-      <c r="G211" t="inlineStr">
-        <is>
-          <t>Au, Ag</t>
-        </is>
-      </c>
-      <c r="H211" t="inlineStr">
-        <is>
-          <t>Past Producer</t>
-        </is>
-      </c>
-      <c r="I211" t="b">
-        <v>0</v>
-      </c>
-      <c r="J211" t="b">
-        <v>0</v>
-      </c>
-      <c r="K211" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L211" t="inlineStr"/>
-      <c r="M211" t="inlineStr"/>
-      <c r="N211" t="inlineStr"/>
-      <c r="O211" t="n">
-        <v>0</v>
-      </c>
-      <c r="P211" t="inlineStr"/>
-      <c r="Q211" t="inlineStr"/>
-      <c r="R211" t="inlineStr"/>
-      <c r="S211" t="n">
-        <v>8</v>
-      </c>
-      <c r="T211" t="n">
-        <v>200</v>
-      </c>
-      <c r="U211" t="n">
-        <v>4</v>
-      </c>
-      <c r="V211" t="n">
-        <v>51.00059</v>
-      </c>
-      <c r="W211" t="n">
-        <v>-95.71872</v>
-      </c>
-      <c r="X211" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
